--- a/output/Amazon_Seller_Master_Data.xlsx
+++ b/output/Amazon_Seller_Master_Data.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amazon Sellers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Amazon Sellers'!$A$1:$U$383</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Amazon Sellers'!$A$1:$U$392</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,14 +484,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U383"/>
+  <dimension ref="A1:U392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="43" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
@@ -507,7 +507,7 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="43" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1">
@@ -37667,8 +37667,881 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" s="3" t="inlineStr">
+        <is>
+          <t>Women's Flats Amazon</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="inlineStr"/>
+      <c r="C384" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D384" s="3" t="inlineStr">
+        <is>
+          <t>Yuvi Royals</t>
+        </is>
+      </c>
+      <c r="E384" s="3" t="inlineStr">
+        <is>
+          <t>Seller</t>
+        </is>
+      </c>
+      <c r="F384" s="3" t="inlineStr">
+        <is>
+          <t>Women'S Flats Amazon</t>
+        </is>
+      </c>
+      <c r="G384" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H384" s="5" t="inlineStr">
+        <is>
+          <t>+919163042833</t>
+        </is>
+      </c>
+      <c r="I384" s="3" t="inlineStr">
+        <is>
+          <t>info@yuvi.co.in</t>
+        </is>
+      </c>
+      <c r="J384" s="5" t="inlineStr">
+        <is>
+          <t>08GSWPS3557L1ZH</t>
+        </is>
+      </c>
+      <c r="K384" s="5" t="inlineStr">
+        <is>
+          <t>GSWPS3557L</t>
+        </is>
+      </c>
+      <c r="L384" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M384" s="6" t="inlineStr">
+        <is>
+          <t>1ST Floor, 14 Joshi Colony Barkat Nager, Tonk Phatak, Jaipur, Raj- Rajasthan 302015</t>
+        </is>
+      </c>
+      <c r="N384" s="3" t="inlineStr"/>
+      <c r="O384" s="3" t="inlineStr">
+        <is>
+          <t>Raj Rajasthan</t>
+        </is>
+      </c>
+      <c r="P384" s="3" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="Q384" s="5" t="inlineStr">
+        <is>
+          <t>302015</t>
+        </is>
+      </c>
+      <c r="R384" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S384" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yuvistyle.com/</t>
+        </is>
+      </c>
+      <c r="T384" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U384" s="3" t="inlineStr">
+        <is>
+          <t>Amazon + Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="3" t="inlineStr">
+        <is>
+          <t>Women's Flats Amazon</t>
+        </is>
+      </c>
+      <c r="B385" s="3" t="inlineStr"/>
+      <c r="C385" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D385" s="3" t="inlineStr">
+        <is>
+          <t>JM LOOKS</t>
+        </is>
+      </c>
+      <c r="E385" s="3" t="inlineStr">
+        <is>
+          <t>Seller</t>
+        </is>
+      </c>
+      <c r="F385" s="3" t="inlineStr">
+        <is>
+          <t>Women'S Flats Amazon</t>
+        </is>
+      </c>
+      <c r="G385" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H385" s="5" t="inlineStr">
+        <is>
+          <t>+919299931199</t>
+        </is>
+      </c>
+      <c r="I385" s="3" t="inlineStr">
+        <is>
+          <t>support@jmlooks.com</t>
+        </is>
+      </c>
+      <c r="J385" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K385" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L385" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M385" s="6" t="inlineStr">
+        <is>
+          <t>SHIV GANGA ENTERPRISES 73/7/3 Basement Floor Part A, Landmark Pillar No.463 &amp; Relaxo Showroom, Near Rajdhani Park Metro Station Delhi 110041</t>
+        </is>
+      </c>
+      <c r="N385" s="3" t="inlineStr"/>
+      <c r="O385" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P385" s="3" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="Q385" s="5" t="inlineStr">
+        <is>
+          <t>110041</t>
+        </is>
+      </c>
+      <c r="R385" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S385" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jmlooks.com/</t>
+        </is>
+      </c>
+      <c r="T385" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U385" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="3" t="inlineStr">
+        <is>
+          <t>Women's Flats Amazon</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="inlineStr"/>
+      <c r="C386" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D386" s="3" t="inlineStr">
+        <is>
+          <t>Fausto Luckystar</t>
+        </is>
+      </c>
+      <c r="E386" s="3" t="inlineStr">
+        <is>
+          <t>Seller</t>
+        </is>
+      </c>
+      <c r="F386" s="3" t="inlineStr">
+        <is>
+          <t>Women'S Flats Amazon</t>
+        </is>
+      </c>
+      <c r="G386" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H386" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I386" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J386" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K386" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L386" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M386" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N386" s="3" t="inlineStr"/>
+      <c r="O386" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P386" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q386" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R386" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S386" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T386" s="3" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="U386" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="3" t="inlineStr">
+        <is>
+          <t>Women's Flats Amazon</t>
+        </is>
+      </c>
+      <c r="B387" s="3" t="inlineStr"/>
+      <c r="C387" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D387" s="3" t="inlineStr">
+        <is>
+          <t>FashionVillage20</t>
+        </is>
+      </c>
+      <c r="E387" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F387" s="3" t="inlineStr">
+        <is>
+          <t>Women'S Flats Amazon</t>
+        </is>
+      </c>
+      <c r="G387" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H387" s="5" t="inlineStr">
+        <is>
+          <t>+918001801961</t>
+        </is>
+      </c>
+      <c r="I387" s="3" t="inlineStr">
+        <is>
+          <t>contact@jaagrukbharat.com</t>
+        </is>
+      </c>
+      <c r="J387" s="5" t="inlineStr">
+        <is>
+          <t>27AAPFU0939F1ZV</t>
+        </is>
+      </c>
+      <c r="K387" s="5" t="inlineStr">
+        <is>
+          <t>AAPFU0939F</t>
+        </is>
+      </c>
+      <c r="L387" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M387" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N387" s="3" t="inlineStr"/>
+      <c r="O387" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P387" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q387" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R387" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S387" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T387" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U387" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="3" t="inlineStr">
+        <is>
+          <t>Women's Flats Amazon</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="inlineStr"/>
+      <c r="C388" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D388" s="3" t="inlineStr">
+        <is>
+          <t>Ishan Traders .</t>
+        </is>
+      </c>
+      <c r="E388" s="3" t="inlineStr">
+        <is>
+          <t>Seller</t>
+        </is>
+      </c>
+      <c r="F388" s="3" t="inlineStr">
+        <is>
+          <t>Women'S Flats Amazon</t>
+        </is>
+      </c>
+      <c r="G388" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H388" s="5" t="inlineStr">
+        <is>
+          <t>+914909002025</t>
+        </is>
+      </c>
+      <c r="I388" s="3" t="inlineStr">
+        <is>
+          <t>support@ishantraders.com</t>
+        </is>
+      </c>
+      <c r="J388" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K388" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L388" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M388" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N388" s="3" t="inlineStr"/>
+      <c r="O388" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P388" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q388" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R388" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S388" s="3" t="inlineStr">
+        <is>
+          <t>https://ishantraders.in/</t>
+        </is>
+      </c>
+      <c r="T388" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U388" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="3" t="inlineStr">
+        <is>
+          <t>Women's Flats Amazon</t>
+        </is>
+      </c>
+      <c r="B389" s="3" t="inlineStr"/>
+      <c r="C389" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D389" s="3" t="inlineStr">
+        <is>
+          <t>Desire Footwears Creations</t>
+        </is>
+      </c>
+      <c r="E389" s="3" t="inlineStr">
+        <is>
+          <t>Seller</t>
+        </is>
+      </c>
+      <c r="F389" s="3" t="inlineStr">
+        <is>
+          <t>Women'S Flats Amazon</t>
+        </is>
+      </c>
+      <c r="G389" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H389" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I389" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J389" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K389" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L389" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M389" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N389" s="3" t="inlineStr"/>
+      <c r="O389" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P389" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q389" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R389" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S389" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T389" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U389" s="3" t="inlineStr">
+        <is>
+          <t>Amazon + Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="3" t="inlineStr">
+        <is>
+          <t>Women'S Flats Amazon</t>
+        </is>
+      </c>
+      <c r="B390" s="3" t="inlineStr"/>
+      <c r="C390" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D390" s="3" t="inlineStr">
+        <is>
+          <t>TRASE</t>
+        </is>
+      </c>
+      <c r="E390" s="3" t="inlineStr">
+        <is>
+          <t>Seller</t>
+        </is>
+      </c>
+      <c r="F390" s="3" t="inlineStr">
+        <is>
+          <t>Women'S Flats Amazon</t>
+        </is>
+      </c>
+      <c r="G390" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H390" s="5" t="inlineStr">
+        <is>
+          <t>+914235892026</t>
+        </is>
+      </c>
+      <c r="I390" s="3" t="inlineStr">
+        <is>
+          <t>care@trase.in</t>
+        </is>
+      </c>
+      <c r="J390" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K390" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L390" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M390" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N390" s="3" t="inlineStr"/>
+      <c r="O390" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P390" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q390" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R390" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S390" s="3" t="inlineStr">
+        <is>
+          <t>https://www.trase.in/</t>
+        </is>
+      </c>
+      <c r="T390" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U390" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="3" t="inlineStr">
+        <is>
+          <t>Women's Flats Amazon</t>
+        </is>
+      </c>
+      <c r="B391" s="3" t="inlineStr"/>
+      <c r="C391" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D391" s="3" t="inlineStr">
+        <is>
+          <t>Cocoblu Retail</t>
+        </is>
+      </c>
+      <c r="E391" s="3" t="inlineStr">
+        <is>
+          <t>Seller</t>
+        </is>
+      </c>
+      <c r="F391" s="3" t="inlineStr">
+        <is>
+          <t>Women'S Flats Amazon</t>
+        </is>
+      </c>
+      <c r="G391" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H391" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I391" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J391" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K391" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L391" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M391" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N391" s="3" t="inlineStr"/>
+      <c r="O391" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P391" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q391" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R391" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S391" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T391" s="3" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="U391" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="3" t="inlineStr">
+        <is>
+          <t>Women's Flats Amazon</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="inlineStr"/>
+      <c r="C392" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D392" s="3" t="inlineStr">
+        <is>
+          <t>H.V Global</t>
+        </is>
+      </c>
+      <c r="E392" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F392" s="3" t="inlineStr">
+        <is>
+          <t>Women'S Flats Amazon</t>
+        </is>
+      </c>
+      <c r="G392" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H392" s="5" t="inlineStr">
+        <is>
+          <t>+919217326570</t>
+        </is>
+      </c>
+      <c r="I392" s="3" t="inlineStr">
+        <is>
+          <t>schdv@yahoo.com</t>
+        </is>
+      </c>
+      <c r="J392" s="5" t="inlineStr">
+        <is>
+          <t>03AAACH7298C4ZO</t>
+        </is>
+      </c>
+      <c r="K392" s="5" t="inlineStr">
+        <is>
+          <t>AAACH7298C</t>
+        </is>
+      </c>
+      <c r="L392" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M392" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N392" s="3" t="inlineStr"/>
+      <c r="O392" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P392" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q392" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R392" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S392" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hollingsworth-vose.com/</t>
+        </is>
+      </c>
+      <c r="T392" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U392" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U383"/>
+  <autoFilter ref="A1:U392"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
